--- a/tests/testthat/fixtures/crosstab/XX1234567_0_XTAB.xlsx
+++ b/tests/testthat/fixtures/crosstab/XX1234567_0_XTAB.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Matrix:</t>
   </si>
@@ -23,24 +23,33 @@
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">Sample Type:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG</t>
+  </si>
+  <si>
     <t xml:space="preserve">Workgroup:</t>
   </si>
   <si>
     <t xml:space="preserve">XX1234567</t>
   </si>
   <si>
+    <t xml:space="preserve">ALS Sample Number:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XX1234567001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XX1234567002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Project name/number:</t>
   </si>
   <si>
     <t xml:space="preserve">Test Project A / XX1234567</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample Type:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REG</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sample Date:</t>
   </si>
   <si>
@@ -56,121 +65,55 @@
     <t xml:space="preserve">T.S02</t>
   </si>
   <si>
-    <t xml:space="preserve">T.MW01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depth (m):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALS Sample Number:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XX1234567001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XX1234567002</t>
+    <t xml:space="preserve">Site:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyte grouping/Analyte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAS Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limit of reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA005P: pH by PC Titrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pH Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOIL</t>
   </si>
   <si>
     <t xml:space="preserve">XX1234567003</t>
   </si>
   <si>
-    <t xml:space="preserve">Analyte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAS Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limit of reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA005P: pH by PC Titrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">----</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EK040P: Fluoride by PC Titrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluoride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16984-48-8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mg/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt;2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA010P: Conductivity by PC Titrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Conductivity @ 25°C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">µS/cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOIL</t>
-  </si>
-  <si>
     <t xml:space="preserve">25/05/2025</t>
   </si>
   <si>
     <t xml:space="preserve">T.S03</t>
   </si>
   <si>
-    <t xml:space="preserve">XX1234567004</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical Conductivity (25C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uS/cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210</t>
   </si>
 </sst>
 </file>
@@ -510,67 +453,67 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -579,21 +522,21 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
@@ -602,21 +545,21 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>2</v>
@@ -628,27 +571,27 @@
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
         <v>2</v>
@@ -671,30 +614,30 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
         <v>2</v>
@@ -714,39 +657,39 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="G11" t="s">
         <v>2</v>
@@ -754,22 +697,22 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>2</v>
       </c>
       <c r="G12" t="s">
         <v>2</v>
@@ -777,30 +720,30 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
         <v>31</v>
       </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -809,13 +752,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
         <v>2</v>
@@ -823,22 +766,22 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G15" t="s">
         <v>2</v>
@@ -846,16 +789,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
         <v>2</v>
@@ -869,10 +812,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
         <v>2</v>
@@ -892,7 +835,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -904,7 +847,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F18" t="s">
         <v>2</v>
@@ -915,231 +858,24 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F19" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G19" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F22" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F25" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" t="s">
-        <v>51</v>
-      </c>
-      <c r="D28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F28" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" t="s">
         <v>2</v>
       </c>
     </row>
